--- a/results/tab02-1.xlsx
+++ b/results/tab02-1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>H21(OLS)+geo+country+region</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>H21(RLM)+full</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>H21(RLM)+geo</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>H21(RLM)+geo+country</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>H21(RLM)+geo+country+region</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>H21(MLM)+geo+country</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>H21(MLM)+geo+country+region</t>
         </is>
@@ -484,29 +494,41 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>0.858***
+[0.805, 0.910]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.507***
 [0.492, 0.523]</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.709***
 [0.664, 0.754]</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.721***
 [0.673, 0.770]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.879***
+[0.829, 0.929]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.723***
 [0.664, 0.782]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.682***
 [0.635, 0.729]</t>
@@ -539,29 +561,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.112***
+[0.094, 0.130]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.128***
 [0.121, 0.135]</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.091***
 [0.073, 0.109]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.091***
 [0.073, 0.109]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.101***
+[0.084, 0.119]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.119***
 [0.100, 0.137]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.133***
 [0.116, 0.151]</t>
@@ -582,43 +616,60 @@
 [-0.000, 0.000]</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.000
+[-0.000, 0.000]</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>-0.000
 [-0.001, 0.000]</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.000
+[-0.001, 0.000]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Country Var.</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-0.001***
+[-0.001, -0.001]</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.015
-(0.008)</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.001***
+[-0.001, -0.001]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Region Var.</t>
+          <t>Country Var.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -628,56 +679,92 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.020
-(0.006)</t>
-        </is>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.015
+(0.008)</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Region Var.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.020
+(0.006)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>R² = .04, R²adj = .04, F(1, 35480) = 1451.17, p &lt; .0001, AIC = 38587.8, BIC = 38604.7, LL = -19291.9, MAE = 0.330, MAD = 0.413, N = 35481</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>R² = .01, R²adj = .01, F(1, 7916) = 110.73, p &lt; .0001, AIC = 12402.2, BIC = 12416.2, LL = -6199.1, MAE = 0.425, MAD = 0.542, N = 7917</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>R² = .01, R²adj = .01, F(2, 7915) = 55.46, p &lt; .0001, AIC = 12404.0, BIC = 12424.9, LL = -6199.0, MAE = 0.425, MAD = 0.541, N = 7917</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>R² = .05, R²adj = .05, F(3, 7914) = 130.79, p &lt; .0001, AIC = 12133.0, BIC = 12161.0, LL = -6062.5, MAE = 0.413, MAD = 0.512, N = 7917</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>R² = .04, R²adj = .04, F(1, 35480) = 1492.80, p &lt; .0001, MAE = 0.327, MAD = 0.390, N = 35481</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>R² = .01, R²adj = .01, F(1, 7916) = 105.49, p &lt; .0001, MAE = 0.423, MAD = 0.522, N = 7917</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>R² = .01, R²adj = .01, F(2, 7915) = 53.57, p &lt; .0001, MAE = 0.423, MAD = 0.523, N = 7917</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>R² = .05, R²adj = .05, F(3, 7914) = 146.71, p &lt; .0001, MAE = 0.409, MAD = 0.482, N = 7917</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>R² = .07, R²adj = .07, F(1, 7916) = 611.93, p &lt; .0001, AIC = 11991.0, BIC = 12018.9, LL = -5991.5, MAE = 0.403, MAD = 0.492, N = 7917, G = 97,
  ICC = 0.05, LRTstat. = 26600.8 (p &lt; .0001)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>R² = .10, R²adj = .10, F(1, 7916) = 878.09, p &lt; .0001, AIC = 11475.2, BIC = 11510.1, LL = -5732.6, MAE = 0.375, MAD = 0.420, N = 7917, G = 97,
  ICC = 0.00, LRTstat. = 26600.8 (p &lt; .0001)</t>

--- a/results/tab02-1.xlsx
+++ b/results/tab02-1.xlsx
@@ -476,8 +476,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.502***
-[0.486, 0.519]</t>
+          <t>0.488***
+[0.472, 0.505]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,8 +500,8 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.507***
-[0.492, 0.523]</t>
+          <t>0.481***
+[0.465, 0.498]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -543,8 +543,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.138***
-[0.131, 0.145]</t>
+          <t>0.130***
+[0.123, 0.137]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,8 +567,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.128***
-[0.121, 0.135]</t>
+          <t>0.127***
+[0.120, 0.134]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R² = .04, R²adj = .04, F(1, 35480) = 1451.17, p &lt; .0001, AIC = 38587.8, BIC = 38604.7, LL = -19291.9, MAE = 0.330, MAD = 0.413, N = 35481</t>
+          <t>R² = .04, R²adj = .04, F(1, 27563) = 1198.38, p &lt; .0001, AIC = 23774.1, BIC = 23790.5, LL = -11885.1, MAE = 0.298, MAD = 0.373, N = 27564</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R² = .04, R²adj = .04, F(1, 35480) = 1492.80, p &lt; .0001, MAE = 0.327, MAD = 0.390, N = 35481</t>
+          <t>R² = .05, R²adj = .05, F(1, 27563) = 1308.17, p &lt; .0001, MAE = 0.296, MAD = 0.353, N = 27564</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">

--- a/results/tab02-1.xlsx
+++ b/results/tab02-1.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>H21(OLS)+full</t>
+          <t>H21(OLS)+nogeo</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>H21(RLM)+full</t>
+          <t>H21(RLM)+nogeo</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
